--- a/LangMod/JP/Quests.xlsx
+++ b/LangMod/JP/Quests.xlsx
@@ -429,8 +429,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">Are you good at crafting? I want to prepare #1 as a gift for an important friend, but if possible, I want it to be something special. Please make a #1 of #2 and #3. 
-Recently, </t>
+      <t xml:space="preserve">Are you good at crafting? I want to prepare #1 as a gift for an important </t>
     </r>
     <r>
       <rPr>
@@ -450,33 +449,9 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve"> of mine bragged about having a rare #1. It’s frustrating! I really want a #1 like that too! So, please make a #1 of #2 and #3 and bring it to me. </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">byakko_mod_guild_merchant_deliver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高速輸送依頼
-よくある配送ミス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Express transport request
-Delivery mistakes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuestMGDeliver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">merchant,needDestZone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
+      <t xml:space="preserve">, but if possible, I want it to be something special. Please make a #1 of #2 and #3. 
+Recently, </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -485,6 +460,51 @@
         <family val="0"/>
         <charset val="128"/>
       </rPr>
+      <t xml:space="preserve">[qFriend]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> of mine bragged about having a rare #1. It’s frustrating! I really want a #1 like that too! So, please make a #1 of #2 and #3 and bring it to me. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">byakko_mod_guild_merchant_deliver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高速輸送依頼
+よくある配送ミス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Express transport request
+Delivery mistakes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuestMGDeliver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">merchant,needDestZone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
       <t xml:space="preserve">#3に住む[qClient]に#2を届ける約束をしていたの{だが}、調達が遅れて{I}の足では</t>
     </r>
     <r>
@@ -510,8 +530,57 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">I had promised to deliver #2 to my father who lives in #3, but the procurement was delayed, and it looks like I won’t make it in time on foot. Use a return spell, a teleporter, or whatever you need—just hurry and take it to him.
-Damn it, my father in #3 asked me for #2, but it seems I delivered less than he requested. Take the additional amount to him immediately. </t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">I had promised to deliver #2 to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">[qClient]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> who lives in #3, but the procurement was delayed, and it looks like I won’t make it in time on foot. Use a return spell, a teleporter, or whatever you need—just hurry and take it to him.
+Damn it, my </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">[qClient]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> in #3 asked me for #2, but it seems I delivered less than he requested. Take the additional amount to him immediately. </t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">byakko_mod_guild_merchant_escort</t>
@@ -4151,7 +4220,7 @@
         <v>92</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="L29" s="7" t="s">
         <v>206</v>
@@ -4214,7 +4283,7 @@
         <v>92</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="L30" s="15" t="s">
         <v>214</v>
@@ -4333,7 +4402,7 @@
         <v>92</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>227</v>
